--- a/backend/data/financials_by_company/1DWNI.MI.xlsx
+++ b/backend/data/financials_by_company/1DWNI.MI.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC5"/>
+  <dimension ref="A1:BC6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -697,221 +697,129 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>-46995000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-39600000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-313300000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-313300000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>-617200000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>39600000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>865800000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-352900000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-392500000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-156700000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>175400000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>22400000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>-350895000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>-590500000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>604100000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>3300000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>396934985</v>
+        <v>358497720</v>
       </c>
       <c r="T2" t="n">
-        <v>396934985</v>
+        <v>358497720</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.49</v>
+        <v>2.45</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.49</v>
-      </c>
-      <c r="W2" t="n">
-        <v>-590500000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-590500000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-590500000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>500000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-591000000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>26700000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>-617700000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>49800000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-567900000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-318100000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-38100000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>392900000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>-36700000</v>
-      </c>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="n">
-        <v>-156700000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>3700000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>175400000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>22400000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>574800000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>-261700000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>18400000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>27500000</v>
-      </c>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="n">
-        <v>27500000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>119100000</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>2700000</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>116400000</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>3300000</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>313100000</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>865800000</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>1178900000</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>1178900000</v>
-      </c>
+        <v>2.45</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="n">
+        <v>27800000</v>
+      </c>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="n">
+        <v>179200000</v>
+      </c>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-12847000</v>
+        <v>13915200</v>
       </c>
       <c r="C3" t="n">
-        <v>0.29</v>
+        <v>0.312</v>
       </c>
       <c r="D3" t="n">
-        <v>-2900200000</v>
+        <v>-388700000</v>
       </c>
       <c r="E3" t="n">
-        <v>-44300000</v>
+        <v>44600000</v>
       </c>
       <c r="F3" t="n">
-        <v>-44300000</v>
+        <v>44600000</v>
       </c>
       <c r="G3" t="n">
-        <v>-2364100000</v>
+        <v>-401300000</v>
       </c>
       <c r="H3" t="n">
-        <v>305000000</v>
+        <v>146800000</v>
       </c>
       <c r="I3" t="n">
-        <v>683100000</v>
+        <v>604900000</v>
       </c>
       <c r="J3" t="n">
-        <v>-2944500000</v>
+        <v>-344100000</v>
       </c>
       <c r="K3" t="n">
-        <v>-3249500000</v>
+        <v>-490900000</v>
       </c>
       <c r="L3" t="n">
-        <v>-148700000</v>
+        <v>-80400000</v>
       </c>
       <c r="M3" t="n">
-        <v>169800000</v>
+        <v>109300000</v>
       </c>
       <c r="N3" t="n">
-        <v>27900000</v>
+        <v>30500000</v>
       </c>
       <c r="O3" t="n">
-        <v>-2332647000</v>
+        <v>-431984800</v>
       </c>
       <c r="P3" t="n">
-        <v>-2697600000</v>
+        <v>-434100000</v>
       </c>
       <c r="Q3" t="n">
-        <v>552000000</v>
+        <v>485300000</v>
       </c>
       <c r="R3" t="n">
-        <v>3000000</v>
+        <v>1500000</v>
       </c>
       <c r="S3" t="n">
         <v>396934985</v>
@@ -920,163 +828,161 @@
         <v>396934985</v>
       </c>
       <c r="U3" t="n">
-        <v>-6.8</v>
+        <v>-1.09</v>
       </c>
       <c r="V3" t="n">
-        <v>-6.8</v>
+        <v>-1.09</v>
       </c>
       <c r="W3" t="n">
-        <v>-2697600000</v>
+        <v>-434100000</v>
       </c>
       <c r="X3" t="n">
-        <v>-2697600000</v>
+        <v>-434100000</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>-2697600000</v>
+        <v>-434100000</v>
       </c>
       <c r="AA3" t="n">
-        <v>63500000</v>
+        <v>11600000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-2761100000</v>
+        <v>-445700000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-333500000</v>
+        <v>-32800000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-2427600000</v>
+        <v>-412900000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-991700000</v>
+        <v>-187300000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-3419300000</v>
+        <v>-600200000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-25900000</v>
+        <v>4100000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-25500000</v>
+        <v>-28800000</v>
       </c>
       <c r="AI3" t="n">
-        <v>51400000</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
+        <v>24900000</v>
+      </c>
+      <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>-200000</v>
       </c>
       <c r="AL3" t="n">
-        <v>-148700000</v>
+        <v>-80400000</v>
       </c>
       <c r="AM3" t="n">
-        <v>6800000</v>
+        <v>1600000</v>
       </c>
       <c r="AN3" t="n">
-        <v>169800000</v>
+        <v>109300000</v>
       </c>
       <c r="AO3" t="n">
-        <v>27900000</v>
+        <v>30500000</v>
       </c>
       <c r="AP3" t="n">
-        <v>512200000</v>
+        <v>381000000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-131100000</v>
+        <v>-119600000</v>
       </c>
       <c r="AR3" t="n">
-        <v>5300000</v>
+        <v>67700000</v>
       </c>
       <c r="AS3" t="n">
-        <v>107500000</v>
+        <v>140100000</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AU3" t="n">
-        <v>107500000</v>
+        <v>140100000</v>
       </c>
       <c r="AV3" t="n">
-        <v>126300000</v>
+        <v>26500000</v>
       </c>
       <c r="AW3" t="n">
-        <v>4700000</v>
+        <v>2600000</v>
       </c>
       <c r="AX3" t="n">
-        <v>121600000</v>
+        <v>23900000</v>
       </c>
       <c r="AY3" t="n">
-        <v>3000000</v>
+        <v>1500000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>381100000</v>
+        <v>261400000</v>
       </c>
       <c r="BA3" t="n">
-        <v>683100000</v>
+        <v>604900000</v>
       </c>
       <c r="BB3" t="n">
-        <v>1064200000</v>
+        <v>866300000</v>
       </c>
       <c r="BC3" t="n">
-        <v>1064200000</v>
+        <v>866300000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>13915200</v>
+        <v>-12847000</v>
       </c>
       <c r="C4" t="n">
-        <v>0.312</v>
+        <v>0.29</v>
       </c>
       <c r="D4" t="n">
-        <v>-388700000</v>
+        <v>-2900200000</v>
       </c>
       <c r="E4" t="n">
-        <v>44600000</v>
+        <v>-44300000</v>
       </c>
       <c r="F4" t="n">
-        <v>44600000</v>
+        <v>-44300000</v>
       </c>
       <c r="G4" t="n">
-        <v>-401300000</v>
+        <v>-2364100000</v>
       </c>
       <c r="H4" t="n">
-        <v>146800000</v>
+        <v>305000000</v>
       </c>
       <c r="I4" t="n">
-        <v>604900000</v>
+        <v>683100000</v>
       </c>
       <c r="J4" t="n">
-        <v>-344100000</v>
+        <v>-2944500000</v>
       </c>
       <c r="K4" t="n">
-        <v>-490900000</v>
+        <v>-3249500000</v>
       </c>
       <c r="L4" t="n">
-        <v>-80400000</v>
+        <v>-148700000</v>
       </c>
       <c r="M4" t="n">
-        <v>109300000</v>
+        <v>169800000</v>
       </c>
       <c r="N4" t="n">
-        <v>30500000</v>
+        <v>27900000</v>
       </c>
       <c r="O4" t="n">
-        <v>-431984800</v>
+        <v>-2332647000</v>
       </c>
       <c r="P4" t="n">
-        <v>-434100000</v>
+        <v>-2697600000</v>
       </c>
       <c r="Q4" t="n">
-        <v>485300000</v>
+        <v>552000000</v>
       </c>
       <c r="R4" t="n">
-        <v>1500000</v>
+        <v>3000000</v>
       </c>
       <c r="S4" t="n">
         <v>396934985</v>
@@ -1085,268 +991,425 @@
         <v>396934985</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.09</v>
+        <v>-6.8</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.09</v>
+        <v>-6.8</v>
       </c>
       <c r="W4" t="n">
-        <v>-434100000</v>
+        <v>-2697600000</v>
       </c>
       <c r="X4" t="n">
-        <v>-434100000</v>
+        <v>-2697600000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>-434100000</v>
+        <v>-2697600000</v>
       </c>
       <c r="AA4" t="n">
-        <v>11600000</v>
+        <v>63500000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-445700000</v>
+        <v>-2761100000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-32800000</v>
+        <v>-333500000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-412900000</v>
+        <v>-2427600000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-187300000</v>
+        <v>-991700000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-600200000</v>
+        <v>-3419300000</v>
       </c>
       <c r="AG4" t="n">
-        <v>4100000</v>
+        <v>-25900000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-28800000</v>
+        <v>-25500000</v>
       </c>
       <c r="AI4" t="n">
-        <v>24900000</v>
-      </c>
-      <c r="AJ4" t="inlineStr"/>
+        <v>51400000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
       <c r="AK4" t="n">
-        <v>-200000</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>-80400000</v>
+        <v>-148700000</v>
       </c>
       <c r="AM4" t="n">
-        <v>1600000</v>
+        <v>6800000</v>
       </c>
       <c r="AN4" t="n">
-        <v>109300000</v>
+        <v>169800000</v>
       </c>
       <c r="AO4" t="n">
-        <v>30500000</v>
+        <v>27900000</v>
       </c>
       <c r="AP4" t="n">
-        <v>381000000</v>
+        <v>512200000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-119600000</v>
+        <v>-131100000</v>
       </c>
       <c r="AR4" t="n">
-        <v>67700000</v>
+        <v>5300000</v>
       </c>
       <c r="AS4" t="n">
-        <v>140100000</v>
+        <v>107500000</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AU4" t="n">
-        <v>140100000</v>
+        <v>107500000</v>
       </c>
       <c r="AV4" t="n">
-        <v>26500000</v>
+        <v>126300000</v>
       </c>
       <c r="AW4" t="n">
-        <v>2600000</v>
+        <v>4700000</v>
       </c>
       <c r="AX4" t="n">
-        <v>23900000</v>
+        <v>121600000</v>
       </c>
       <c r="AY4" t="n">
-        <v>1500000</v>
+        <v>3000000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>261400000</v>
+        <v>381100000</v>
       </c>
       <c r="BA4" t="n">
-        <v>604900000</v>
+        <v>683100000</v>
       </c>
       <c r="BB4" t="n">
-        <v>866300000</v>
+        <v>1064200000</v>
       </c>
       <c r="BC4" t="n">
-        <v>866300000</v>
+        <v>1064200000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-6720000</v>
+        <v>-46995000</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="D5" t="n">
-        <v>2160500000</v>
+        <v>-39600000</v>
       </c>
       <c r="E5" t="n">
-        <v>-22400000</v>
+        <v>-313300000</v>
       </c>
       <c r="F5" t="n">
-        <v>-22400000</v>
+        <v>-313300000</v>
       </c>
       <c r="G5" t="n">
-        <v>877200000</v>
+        <v>-617200000</v>
       </c>
       <c r="H5" t="n">
-        <v>213900000</v>
+        <v>39600000</v>
       </c>
       <c r="I5" t="n">
-        <v>538000000</v>
+        <v>865800000</v>
       </c>
       <c r="J5" t="n">
-        <v>2138100000</v>
+        <v>-352900000</v>
       </c>
       <c r="K5" t="n">
-        <v>1924200000</v>
+        <v>-392500000</v>
       </c>
       <c r="L5" t="n">
-        <v>-496000000</v>
+        <v>-156700000</v>
       </c>
       <c r="M5" t="n">
-        <v>147800000</v>
+        <v>175400000</v>
       </c>
       <c r="N5" t="n">
-        <v>4600000</v>
+        <v>22400000</v>
       </c>
       <c r="O5" t="n">
-        <v>892880000</v>
+        <v>-350895000</v>
       </c>
       <c r="P5" t="n">
-        <v>877200000</v>
+        <v>-590500000</v>
       </c>
       <c r="Q5" t="n">
-        <v>729900000</v>
+        <v>604000000</v>
       </c>
       <c r="R5" t="n">
-        <v>5300000</v>
+        <v>3300000</v>
       </c>
       <c r="S5" t="n">
-        <v>358497720</v>
+        <v>396934985</v>
       </c>
       <c r="T5" t="n">
-        <v>358497720</v>
+        <v>396934985</v>
       </c>
       <c r="U5" t="n">
-        <v>2.45</v>
+        <v>-1.49</v>
       </c>
       <c r="V5" t="n">
-        <v>2.45</v>
+        <v>-1.49</v>
       </c>
       <c r="W5" t="n">
-        <v>877200000</v>
+        <v>-590500000</v>
       </c>
       <c r="X5" t="n">
-        <v>877200000</v>
+        <v>-590500000</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>877200000</v>
+        <v>-590500000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-41800000</v>
+        <v>500000</v>
       </c>
       <c r="AB5" t="n">
-        <v>919000000</v>
-      </c>
-      <c r="AC5" t="inlineStr"/>
+        <v>-591000000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>26700000</v>
+      </c>
       <c r="AD5" t="n">
-        <v>919000000</v>
+        <v>-617700000</v>
       </c>
       <c r="AE5" t="n">
-        <v>857400000</v>
+        <v>49800000</v>
       </c>
       <c r="AF5" t="n">
-        <v>1776400000</v>
+        <v>-567900000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-12600000</v>
+        <v>-318100000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-24400000</v>
+        <v>-38100000</v>
       </c>
       <c r="AI5" t="n">
-        <v>9200000</v>
-      </c>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="n">
-        <v>27800000</v>
-      </c>
+        <v>392900000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>-36700000</v>
+      </c>
+      <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>-496000000</v>
+        <v>-156700000</v>
       </c>
       <c r="AM5" t="n">
-        <v>352800000</v>
+        <v>3700000</v>
       </c>
       <c r="AN5" t="n">
-        <v>147800000</v>
+        <v>175400000</v>
       </c>
       <c r="AO5" t="n">
-        <v>4600000</v>
+        <v>22400000</v>
       </c>
       <c r="AP5" t="n">
+        <v>574900000</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-261800000</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>21000000</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>27500000</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="n">
+        <v>27500000</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>116400000</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>800000</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>115600000</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>3300000</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>313100000</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>865800000</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>1178900000</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>1178900000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>3480000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D6" t="n">
+        <v>824700000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>23200000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>23200000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1075200000</v>
+      </c>
+      <c r="H6" t="n">
         <v>404400000</v>
       </c>
-      <c r="AQ5" t="n">
-        <v>191900000</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>50500000</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>213900000</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>179200000</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>213900000</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>84500000</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>8200000</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>76300000</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>5300000</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>596300000</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>538000000</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>1134300000</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>1134300000</v>
+      <c r="I6" t="n">
+        <v>702000000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>847900000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>443500000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-112700000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>160600000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>55300000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1055480000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1146500000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>978200000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>3800000</v>
+      </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>1146500000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1146500000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1146500000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-33100000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1179600000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>71300000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1108300000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-825400000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>282900000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>35000000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-37000000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>58600000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>-56600000</v>
+      </c>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="n">
+        <v>-112700000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>7400000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>160600000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>55300000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>219800000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>276200000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>88700000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>404300000</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="n">
+        <v>404300000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>127200000</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>800000</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>126400000</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>3800000</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>496000000</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>702000000</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1198000000</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1198000000</v>
       </c>
     </row>
   </sheetData>
@@ -1360,7 +1423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CE5"/>
+  <dimension ref="A1:CE6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1777,242 +1840,114 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>3362003</v>
-      </c>
-      <c r="C2" t="n">
-        <v>396934985</v>
-      </c>
-      <c r="D2" t="n">
-        <v>400296988</v>
-      </c>
-      <c r="E2" t="n">
-        <v>7881400000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>8360700000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>13029700000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>21298000000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1121700000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>13029700000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>92700000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>13030000000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>19815600000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>13411600000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>381600000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>13030000000</v>
-      </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="n">
-        <v>8455700000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>4174700000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>396900000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>396900000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>12948300000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>10872300000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>158600000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>7900000</v>
-      </c>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="n">
-        <v>48500000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>2400000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>3788800000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>6866100000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>80500000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>6785600000</v>
-      </c>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="n">
-        <v>2076000000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>42300000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1494600000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>12200000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1482400000</v>
-      </c>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="n">
-        <v>358000000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>58700000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>105600000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>193700000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>26359900000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>23162200000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="n">
+        <v>3400000</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="n">
+        <v>104800000</v>
+      </c>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="n">
+        <v>149000000</v>
+      </c>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="n">
+        <v>176900000</v>
+      </c>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
-        <v>9700000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>240800000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>8600000</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>24100000</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>36000000</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>36000000</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>131300000</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>131300000</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>22539700000</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>300000</v>
-      </c>
+        <v>1200000</v>
+      </c>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
       <c r="BE2" t="n">
+        <v>148100000</v>
+      </c>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="n">
+        <v>200600000</v>
+      </c>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr"/>
+      <c r="BO2" t="inlineStr"/>
+      <c r="BP2" t="inlineStr"/>
+      <c r="BQ2" t="inlineStr"/>
+      <c r="BR2" t="inlineStr"/>
+      <c r="BS2" t="n">
+        <v>5400000</v>
+      </c>
+      <c r="BT2" t="inlineStr"/>
+      <c r="BU2" t="n">
         <v>0</v>
       </c>
-      <c r="BF2" t="n">
-        <v>150800000</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>-134400000</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>285200000</v>
-      </c>
-      <c r="BI2" t="inlineStr"/>
-      <c r="BJ2" t="n">
-        <v>261000000</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>24200000</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>3197700000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>95100000</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>915200000</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>268000000</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>642700000</v>
-      </c>
-      <c r="BS2" t="inlineStr"/>
-      <c r="BT2" t="n">
-        <v>641700000</v>
-      </c>
-      <c r="BU2" t="inlineStr"/>
-      <c r="BV2" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>549700000</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>133200000</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>200600000</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>-25600000</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>226200000</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>386600000</v>
-      </c>
-      <c r="CC2" t="inlineStr"/>
-      <c r="CD2" t="n">
-        <v>386600000</v>
-      </c>
-      <c r="CE2" t="n">
-        <v>386600000</v>
-      </c>
+      <c r="BV2" t="inlineStr"/>
+      <c r="BW2" t="inlineStr"/>
+      <c r="BX2" t="inlineStr"/>
+      <c r="BY2" t="inlineStr"/>
+      <c r="BZ2" t="inlineStr"/>
+      <c r="CA2" t="inlineStr"/>
+      <c r="CB2" t="inlineStr"/>
+      <c r="CC2" t="n">
+        <v>565000000</v>
+      </c>
+      <c r="CD2" t="inlineStr"/>
+      <c r="CE2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>3362003</v>
@@ -2024,44 +1959,44 @@
         <v>400296988</v>
       </c>
       <c r="E3" t="n">
-        <v>8292200000</v>
+        <v>8758200000</v>
       </c>
       <c r="F3" t="n">
-        <v>8552800000</v>
+        <v>9071100000</v>
       </c>
       <c r="G3" t="n">
-        <v>13610600000</v>
+        <v>16134800000</v>
       </c>
       <c r="H3" t="n">
-        <v>22058800000</v>
+        <v>25242100000</v>
       </c>
       <c r="I3" t="n">
-        <v>2326100000</v>
+        <v>1669300000</v>
       </c>
       <c r="J3" t="n">
-        <v>13610600000</v>
+        <v>16134800000</v>
       </c>
       <c r="K3" t="n">
-        <v>105100000</v>
+        <v>128600000</v>
       </c>
       <c r="L3" t="n">
-        <v>13611100000</v>
+        <v>16299600000</v>
       </c>
       <c r="M3" t="n">
-        <v>21859400000</v>
+        <v>24773800000</v>
       </c>
       <c r="N3" t="n">
-        <v>13998200000</v>
+        <v>16775100000</v>
       </c>
       <c r="O3" t="n">
-        <v>387100000</v>
+        <v>475500000</v>
       </c>
       <c r="P3" t="n">
-        <v>13611100000</v>
+        <v>16299600000</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>9034600000</v>
+        <v>11715600000</v>
       </c>
       <c r="S3" t="n">
         <v>4174700000</v>
@@ -2073,179 +2008,185 @@
         <v>396900000</v>
       </c>
       <c r="V3" t="n">
-        <v>13187800000</v>
+        <v>14755700000</v>
       </c>
       <c r="W3" t="n">
-        <v>12394300000</v>
+        <v>13815000000</v>
       </c>
       <c r="X3" t="n">
-        <v>181100000</v>
+        <v>196300000</v>
       </c>
       <c r="Y3" t="n">
-        <v>7700000</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="n">
-        <v>63900000</v>
+        <v>104600000</v>
       </c>
       <c r="AB3" t="n">
-        <v>2600000</v>
+        <v>19400000</v>
       </c>
       <c r="AC3" t="n">
-        <v>3799400000</v>
+        <v>4906400000</v>
       </c>
       <c r="AD3" t="n">
-        <v>8339600000</v>
+        <v>8588300000</v>
       </c>
       <c r="AE3" t="n">
-        <v>91300000</v>
+        <v>114100000</v>
       </c>
       <c r="AF3" t="n">
-        <v>8248300000</v>
-      </c>
-      <c r="AG3" t="inlineStr"/>
+        <v>8474200000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>104600000</v>
+      </c>
       <c r="AH3" t="n">
-        <v>793500000</v>
+        <v>940700000</v>
       </c>
       <c r="AI3" t="n">
-        <v>51500000</v>
+        <v>54100000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>213200000</v>
+        <v>482800000</v>
       </c>
       <c r="AK3" t="n">
-        <v>13800000</v>
+        <v>14500000</v>
       </c>
       <c r="AL3" t="n">
-        <v>199400000</v>
-      </c>
-      <c r="AM3" t="inlineStr"/>
+        <v>468300000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>220100000</v>
+      </c>
       <c r="AN3" t="n">
-        <v>289000000</v>
+        <v>278900000</v>
       </c>
       <c r="AO3" t="n">
-        <v>16300000</v>
+        <v>13500000</v>
       </c>
       <c r="AP3" t="n">
-        <v>98000000</v>
+        <v>117700000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>174700000</v>
+        <v>147700000</v>
       </c>
       <c r="AR3" t="n">
-        <v>27186000000</v>
+        <v>31530800000</v>
       </c>
       <c r="AS3" t="n">
-        <v>24066400000</v>
+        <v>28920800000</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AU3" t="n">
-        <v>203700000</v>
+        <v>214700000</v>
       </c>
       <c r="AV3" t="n">
-        <v>1100000</v>
+        <v>200000</v>
       </c>
       <c r="AW3" t="n">
-        <v>39400000</v>
+        <v>66400000</v>
       </c>
       <c r="AX3" t="n">
-        <v>33800000</v>
+        <v>39600000</v>
       </c>
       <c r="AY3" t="n">
-        <v>33800000</v>
+        <v>39600000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>126300000</v>
+        <v>208000000</v>
       </c>
       <c r="BA3" t="n">
-        <v>126300000</v>
+        <v>208000000</v>
       </c>
       <c r="BB3" t="n">
-        <v>23021500000</v>
+        <v>27301900000</v>
       </c>
       <c r="BC3" t="n">
-        <v>500000</v>
+        <v>164800000</v>
       </c>
       <c r="BD3" t="n">
-        <v>500000</v>
+        <v>24800000</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>140000000</v>
       </c>
       <c r="BF3" t="n">
-        <v>151500000</v>
+        <v>219600000</v>
       </c>
       <c r="BG3" t="n">
-        <v>-114300000</v>
+        <v>-116500000</v>
       </c>
       <c r="BH3" t="n">
-        <v>265800000</v>
+        <v>336100000</v>
       </c>
       <c r="BI3" t="inlineStr"/>
       <c r="BJ3" t="n">
-        <v>250100000</v>
+        <v>288700000</v>
       </c>
       <c r="BK3" t="n">
-        <v>15700000</v>
+        <v>47400000</v>
       </c>
       <c r="BL3" t="n">
-        <v>3119600000</v>
+        <v>2610000000</v>
       </c>
       <c r="BM3" t="n">
-        <v>129100000</v>
+        <v>143000000</v>
       </c>
       <c r="BN3" t="n">
-        <v>900000</v>
+        <v>200000</v>
       </c>
       <c r="BO3" t="n">
-        <v>844100000</v>
+        <v>2400000</v>
       </c>
       <c r="BP3" t="n">
-        <v>1600000</v>
+        <v>0</v>
       </c>
       <c r="BQ3" t="n">
-        <v>246100000</v>
+        <v>104500000</v>
       </c>
       <c r="BR3" t="n">
-        <v>755300000</v>
-      </c>
-      <c r="BS3" t="inlineStr"/>
+        <v>939600000</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>15600000</v>
+      </c>
       <c r="BT3" t="n">
-        <v>752600000</v>
-      </c>
-      <c r="BU3" t="inlineStr"/>
+        <v>926000000</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>47200000</v>
+      </c>
       <c r="BV3" t="n">
-        <v>2700000</v>
+        <v>13600000</v>
       </c>
       <c r="BW3" t="n">
-        <v>698800000</v>
+        <v>1016300000</v>
       </c>
       <c r="BX3" t="n">
-        <v>145600000</v>
+        <v>187100000</v>
       </c>
       <c r="BY3" t="n">
-        <v>140300000</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>-15500000</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>155800000</v>
-      </c>
+        <v>30000000</v>
+      </c>
+      <c r="BZ3" t="inlineStr"/>
+      <c r="CA3" t="inlineStr"/>
       <c r="CB3" t="n">
-        <v>155500000</v>
-      </c>
-      <c r="CC3" t="inlineStr"/>
+        <v>184300000</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>1019000000</v>
+      </c>
       <c r="CD3" t="n">
-        <v>155500000</v>
+        <v>184300000</v>
       </c>
       <c r="CE3" t="n">
-        <v>155500000</v>
+        <v>184300000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>3362003</v>
@@ -2257,44 +2198,44 @@
         <v>400296988</v>
       </c>
       <c r="E4" t="n">
-        <v>8758200000</v>
+        <v>8292200000</v>
       </c>
       <c r="F4" t="n">
-        <v>9071100000</v>
+        <v>8552800000</v>
       </c>
       <c r="G4" t="n">
-        <v>16134800000</v>
+        <v>13610600000</v>
       </c>
       <c r="H4" t="n">
-        <v>25242100000</v>
+        <v>22058800000</v>
       </c>
       <c r="I4" t="n">
-        <v>1669300000</v>
+        <v>2326100000</v>
       </c>
       <c r="J4" t="n">
-        <v>16134800000</v>
+        <v>13610600000</v>
       </c>
       <c r="K4" t="n">
-        <v>128600000</v>
+        <v>105100000</v>
       </c>
       <c r="L4" t="n">
-        <v>16299600000</v>
+        <v>13611100000</v>
       </c>
       <c r="M4" t="n">
-        <v>24773800000</v>
+        <v>21859400000</v>
       </c>
       <c r="N4" t="n">
-        <v>16775100000</v>
+        <v>13998200000</v>
       </c>
       <c r="O4" t="n">
-        <v>475500000</v>
+        <v>387100000</v>
       </c>
       <c r="P4" t="n">
-        <v>16299600000</v>
+        <v>13611100000</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>11715600000</v>
+        <v>9034600000</v>
       </c>
       <c r="S4" t="n">
         <v>4174700000</v>
@@ -2306,185 +2247,179 @@
         <v>396900000</v>
       </c>
       <c r="V4" t="n">
-        <v>14755700000</v>
+        <v>13187800000</v>
       </c>
       <c r="W4" t="n">
-        <v>13815000000</v>
+        <v>12394300000</v>
       </c>
       <c r="X4" t="n">
-        <v>196300000</v>
+        <v>181100000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>7700000</v>
       </c>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="n">
-        <v>104600000</v>
+        <v>63900000</v>
       </c>
       <c r="AB4" t="n">
-        <v>19400000</v>
+        <v>2600000</v>
       </c>
       <c r="AC4" t="n">
-        <v>4906400000</v>
+        <v>3799400000</v>
       </c>
       <c r="AD4" t="n">
-        <v>8588300000</v>
+        <v>8339600000</v>
       </c>
       <c r="AE4" t="n">
-        <v>114100000</v>
+        <v>91300000</v>
       </c>
       <c r="AF4" t="n">
-        <v>8474200000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>104600000</v>
-      </c>
+        <v>8248300000</v>
+      </c>
+      <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>940700000</v>
+        <v>793500000</v>
       </c>
       <c r="AI4" t="n">
-        <v>54100000</v>
+        <v>51500000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>482800000</v>
+        <v>213200000</v>
       </c>
       <c r="AK4" t="n">
-        <v>14500000</v>
+        <v>13800000</v>
       </c>
       <c r="AL4" t="n">
-        <v>468300000</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>220100000</v>
-      </c>
+        <v>199400000</v>
+      </c>
+      <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="n">
-        <v>278900000</v>
+        <v>289000000</v>
       </c>
       <c r="AO4" t="n">
-        <v>13500000</v>
+        <v>16300000</v>
       </c>
       <c r="AP4" t="n">
-        <v>117700000</v>
+        <v>98000000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>147700000</v>
+        <v>174700000</v>
       </c>
       <c r="AR4" t="n">
-        <v>31530800000</v>
+        <v>27186000000</v>
       </c>
       <c r="AS4" t="n">
-        <v>28920800000</v>
+        <v>24066400000</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AU4" t="n">
-        <v>214700000</v>
+        <v>203700000</v>
       </c>
       <c r="AV4" t="n">
-        <v>200000</v>
+        <v>1100000</v>
       </c>
       <c r="AW4" t="n">
-        <v>66400000</v>
+        <v>39400000</v>
       </c>
       <c r="AX4" t="n">
-        <v>39600000</v>
+        <v>33800000</v>
       </c>
       <c r="AY4" t="n">
-        <v>39600000</v>
+        <v>33800000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>208000000</v>
+        <v>126300000</v>
       </c>
       <c r="BA4" t="n">
-        <v>208000000</v>
+        <v>126300000</v>
       </c>
       <c r="BB4" t="n">
-        <v>27301900000</v>
+        <v>23021500000</v>
       </c>
       <c r="BC4" t="n">
-        <v>164800000</v>
+        <v>500000</v>
       </c>
       <c r="BD4" t="n">
-        <v>24800000</v>
+        <v>500000</v>
       </c>
       <c r="BE4" t="n">
-        <v>140000000</v>
+        <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>219600000</v>
+        <v>151500000</v>
       </c>
       <c r="BG4" t="n">
-        <v>-116500000</v>
+        <v>-114300000</v>
       </c>
       <c r="BH4" t="n">
-        <v>336100000</v>
+        <v>265800000</v>
       </c>
       <c r="BI4" t="inlineStr"/>
       <c r="BJ4" t="n">
-        <v>288700000</v>
+        <v>250100000</v>
       </c>
       <c r="BK4" t="n">
-        <v>47400000</v>
+        <v>15700000</v>
       </c>
       <c r="BL4" t="n">
-        <v>2610000000</v>
+        <v>3119600000</v>
       </c>
       <c r="BM4" t="n">
-        <v>143000000</v>
+        <v>129100000</v>
       </c>
       <c r="BN4" t="n">
-        <v>200000</v>
+        <v>900000</v>
       </c>
       <c r="BO4" t="n">
-        <v>2400000</v>
+        <v>844100000</v>
       </c>
       <c r="BP4" t="n">
-        <v>0</v>
+        <v>1600000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>104500000</v>
+        <v>246100000</v>
       </c>
       <c r="BR4" t="n">
-        <v>939600000</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>15600000</v>
-      </c>
+        <v>755300000</v>
+      </c>
+      <c r="BS4" t="inlineStr"/>
       <c r="BT4" t="n">
-        <v>926000000</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>47200000</v>
-      </c>
+        <v>752600000</v>
+      </c>
+      <c r="BU4" t="inlineStr"/>
       <c r="BV4" t="n">
-        <v>13600000</v>
+        <v>2700000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1016300000</v>
+        <v>698800000</v>
       </c>
       <c r="BX4" t="n">
-        <v>187100000</v>
+        <v>145600000</v>
       </c>
       <c r="BY4" t="n">
-        <v>30000000</v>
-      </c>
-      <c r="BZ4" t="inlineStr"/>
-      <c r="CA4" t="inlineStr"/>
+        <v>140300000</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>-15500000</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>155800000</v>
+      </c>
       <c r="CB4" t="n">
-        <v>184300000</v>
-      </c>
-      <c r="CC4" t="n">
-        <v>1019000000</v>
-      </c>
+        <v>155500000</v>
+      </c>
+      <c r="CC4" t="inlineStr"/>
       <c r="CD4" t="n">
-        <v>184300000</v>
+        <v>155500000</v>
       </c>
       <c r="CE4" t="n">
-        <v>184300000</v>
+        <v>155500000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>3362003</v>
@@ -2496,49 +2431,47 @@
         <v>400296988</v>
       </c>
       <c r="E5" t="n">
-        <v>8961900000</v>
+        <v>7881400000</v>
       </c>
       <c r="F5" t="n">
-        <v>9778200000</v>
+        <v>8360700000</v>
       </c>
       <c r="G5" t="n">
-        <v>16546500000</v>
+        <v>13029700000</v>
       </c>
       <c r="H5" t="n">
-        <v>26365900000</v>
+        <v>21298000000</v>
       </c>
       <c r="I5" t="n">
-        <v>2419000000</v>
+        <v>1121700000</v>
       </c>
       <c r="J5" t="n">
-        <v>16546500000</v>
+        <v>13029700000</v>
       </c>
       <c r="K5" t="n">
-        <v>139600000</v>
+        <v>92700000</v>
       </c>
       <c r="L5" t="n">
-        <v>16727300000</v>
+        <v>13030000000</v>
       </c>
       <c r="M5" t="n">
-        <v>26088800000</v>
+        <v>19815600000</v>
       </c>
       <c r="N5" t="n">
-        <v>17203400000</v>
+        <v>13411600000</v>
       </c>
       <c r="O5" t="n">
-        <v>476100000</v>
+        <v>381600000</v>
       </c>
       <c r="P5" t="n">
-        <v>16727300000</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3400000</v>
-      </c>
+        <v>13030000000</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>11907600000</v>
+        <v>8455700000</v>
       </c>
       <c r="S5" t="n">
-        <v>4433400000</v>
+        <v>4174700000</v>
       </c>
       <c r="T5" t="n">
         <v>396900000</v>
@@ -2547,182 +2480,407 @@
         <v>396900000</v>
       </c>
       <c r="V5" t="n">
-        <v>16028800000</v>
+        <v>12948300000</v>
       </c>
       <c r="W5" t="n">
-        <v>15028100000</v>
+        <v>10872300000</v>
       </c>
       <c r="X5" t="n">
-        <v>199000000</v>
+        <v>158600000</v>
       </c>
       <c r="Y5" t="n">
-        <v>23800000</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>104800000</v>
-      </c>
+        <v>7900000</v>
+      </c>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="n">
+        <v>48500000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3788800000</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>6866100000</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>80500000</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>6785600000</v>
+      </c>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="n">
+        <v>2076000000</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>42300000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1494600000</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>12200000</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1482400000</v>
+      </c>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="n">
+        <v>358000000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>58700000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>105600000</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>193700000</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>26359900000</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>23162200000</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>9700000</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>240800000</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>8600000</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>24100000</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>36000000</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>36000000</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>131300000</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>131300000</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>22539700000</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>300000</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>300000</v>
+      </c>
+      <c r="BE5" t="n">
         <v>0</v>
       </c>
-      <c r="AB5" t="n">
-        <v>19400000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>5156600000</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>9480300000</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>118800000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>9361500000</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>149000000</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1000700000</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>94400000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>297900000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>20800000</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>277100000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>176900000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>314100000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>33200000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>126200000</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>314100000</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>33232200000</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>29812500000</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="AU5" t="n">
+      <c r="BF5" t="n">
+        <v>150800000</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>-134400000</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>285200000</v>
+      </c>
+      <c r="BI5" t="inlineStr"/>
+      <c r="BJ5" t="n">
+        <v>261000000</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>24200000</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>3197700000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>95100000</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>915200000</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>268000000</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>642700000</v>
+      </c>
+      <c r="BS5" t="inlineStr"/>
+      <c r="BT5" t="n">
+        <v>641700000</v>
+      </c>
+      <c r="BU5" t="inlineStr"/>
+      <c r="BV5" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>549700000</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>133200000</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>200600000</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>-13500000</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>214100000</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>386600000</v>
+      </c>
+      <c r="CC5" t="inlineStr"/>
+      <c r="CD5" t="n">
+        <v>386600000</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>386600000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>3362003</v>
+      </c>
+      <c r="C6" t="n">
+        <v>396934985</v>
+      </c>
+      <c r="D6" t="n">
+        <v>400296988</v>
+      </c>
+      <c r="E6" t="n">
+        <v>7080400000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>7608900000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>14161900000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>21686100000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-108600000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>14161900000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86300000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>14163500000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>20793000000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>14594800000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>431300000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>14163500000</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="n">
+        <v>9590400000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4174700000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>396900000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>396900000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>11767300000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>9891800000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>178000000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>5300000</v>
+      </c>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="n">
+        <v>46900000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2955100000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>6704700000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>75200000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>6629500000</v>
+      </c>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="n">
+        <v>1875500000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>495800000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>904200000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>11100000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>893100000</v>
+      </c>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="n">
+        <v>339600000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>39700000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>91000000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>208900000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>26362100000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>24595200000</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="n">
+        <v>5700000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>2200000</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>16700000</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>29700000</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>29700000</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>98300000</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>98300000</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>24188300000</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="n">
+        <v>137200000</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>-149600000</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>286800000</v>
+      </c>
+      <c r="BI6" t="inlineStr"/>
+      <c r="BJ6" t="n">
+        <v>256900000</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>29900000</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1766900000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>104900000</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>600000</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>45100000</v>
+      </c>
+      <c r="BP6" t="n">
         <v>0</v>
       </c>
-      <c r="AV5" t="n">
-        <v>100000</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>33900000</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>33900000</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>373300000</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>373300000</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>28730500000</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>180800000</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>32700000</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>148100000</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>202400000</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>-108100000</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>310500000</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>200600000</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>256500000</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>54000000</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>3419700000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>100400000</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>1633300000</v>
-      </c>
-      <c r="BP5" t="inlineStr"/>
-      <c r="BQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>202400000</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>5400000</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>197000000</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV5" t="inlineStr"/>
-      <c r="BW5" t="n">
-        <v>564000000</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>127300000</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>113000000</v>
-      </c>
-      <c r="BZ5" t="inlineStr"/>
-      <c r="CA5" t="inlineStr"/>
-      <c r="CB5" t="n">
-        <v>676700000</v>
-      </c>
-      <c r="CC5" t="n">
-        <v>565000000</v>
-      </c>
-      <c r="CD5" t="n">
-        <v>676700000</v>
-      </c>
-      <c r="CE5" t="n">
-        <v>676700000</v>
+      <c r="BQ6" t="n">
+        <v>60200000</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>747500000</v>
+      </c>
+      <c r="BS6" t="inlineStr"/>
+      <c r="BT6" t="n">
+        <v>745500000</v>
+      </c>
+      <c r="BU6" t="inlineStr"/>
+      <c r="BV6" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>119900000</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>168300000</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>75100000</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>-12500000</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>87600000</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>442200000</v>
+      </c>
+      <c r="CC6" t="inlineStr"/>
+      <c r="CD6" t="n">
+        <v>442200000</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>442200000</v>
       </c>
     </row>
   </sheetData>
@@ -2736,7 +2894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS5"/>
+  <dimension ref="A1:AS6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2963,474 +3121,533 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>725500000</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="n">
-        <v>-223000000</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="n">
-        <v>388600000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-43500000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>201500000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>230600000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-417100000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>1354400000</v>
+      </c>
+      <c r="F2" t="n">
+        <v>660800000</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>-3200000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>-154600000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>-16500000</v>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="n">
-        <v>-223000000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>-223000000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>-223000000</v>
-      </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="n">
-        <v>-77800000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>181000000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>34800000</v>
-      </c>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="n">
-        <v>-291200000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>330200000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-621400000</v>
-      </c>
+        <v>1314700000</v>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="n">
+        <v>660800000</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>660800000</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="n">
+        <v>1354400000</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="n">
+        <v>9700000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>9700000</v>
+      </c>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="n">
-        <v>-2400000</v>
-      </c>
-      <c r="AE2" t="inlineStr"/>
+        <v>9800000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>9800000</v>
+      </c>
       <c r="AF2" t="n">
-        <v>-2400000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>725500000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-79700000</v>
-      </c>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="n">
-        <v>131400000</v>
-      </c>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="n">
-        <v>536600000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>51700000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>39600000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>39600000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>636900000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>-591000000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="n">
+        <v>9700000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>-151800000</v>
+      </c>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="n">
+        <v>-13300000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>-800000</v>
+      </c>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>384800000</v>
+        <v>364900000</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>-472900000</v>
+        <v>-735500000</v>
       </c>
       <c r="E3" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="F3" t="n">
         <v>0</v>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>157100000</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-44400000</v>
-      </c>
+        <v>184300000</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>184300000</v>
+        <v>676700000</v>
       </c>
       <c r="J3" t="n">
-        <v>17200000</v>
+        <v>-492400000</v>
       </c>
       <c r="K3" t="n">
-        <v>-658900000</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
+        <v>-862500000</v>
+      </c>
+      <c r="L3" t="n">
+        <v>40000000</v>
+      </c>
       <c r="M3" t="n">
-        <v>-148800000</v>
+        <v>-118700000</v>
       </c>
       <c r="N3" t="n">
-        <v>-16500000</v>
-      </c>
-      <c r="O3" t="inlineStr"/>
+        <v>-15900000</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
       <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
       <c r="R3" t="n">
-        <v>-472900000</v>
+        <v>-695500000</v>
       </c>
       <c r="S3" t="n">
-        <v>-472900000</v>
+        <v>-695500000</v>
       </c>
       <c r="T3" t="n">
-        <v>-472900000</v>
+        <v>-735500000</v>
       </c>
       <c r="U3" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="V3" t="n">
+        <v>5200000</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-917200000</v>
+      </c>
+      <c r="X3" t="n">
+        <v>37000000</v>
+      </c>
+      <c r="Y3" t="n">
         <v>0</v>
       </c>
-      <c r="V3" t="n">
-        <v>291300000</v>
-      </c>
-      <c r="W3" t="n">
-        <v>569000000</v>
-      </c>
-      <c r="X3" t="n">
-        <v>60500000</v>
-      </c>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
       <c r="AA3" t="n">
-        <v>-338200000</v>
+        <v>885400000</v>
       </c>
       <c r="AB3" t="n">
-        <v>18600000</v>
+        <v>1684900000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-356800000</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
+        <v>-799500000</v>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="n">
-        <v>384800000</v>
+        <v>364900000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-46700000</v>
+        <v>-157800000</v>
       </c>
       <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="n">
-        <v>-219900000</v>
+        <v>-81500000</v>
       </c>
       <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="n">
-        <v>193800000</v>
+        <v>180400000</v>
       </c>
       <c r="AO3" t="n">
-        <v>-998900000</v>
+        <v>-190000000</v>
       </c>
       <c r="AP3" t="n">
-        <v>305000000</v>
+        <v>146800000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>305000000</v>
+        <v>146800000</v>
       </c>
       <c r="AR3" t="n">
-        <v>3912600000</v>
+        <v>912700000</v>
       </c>
       <c r="AS3" t="n">
-        <v>-2761100000</v>
+        <v>-445700000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>364900000</v>
+        <v>384800000</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>-735500000</v>
+        <v>-472900000</v>
       </c>
       <c r="E4" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="F4" t="n">
         <v>0</v>
       </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
+        <v>157100000</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-44400000</v>
+      </c>
+      <c r="I4" t="n">
         <v>184300000</v>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="n">
-        <v>676700000</v>
-      </c>
       <c r="J4" t="n">
-        <v>-492400000</v>
+        <v>17200000</v>
       </c>
       <c r="K4" t="n">
-        <v>-862500000</v>
-      </c>
-      <c r="L4" t="n">
-        <v>40000000</v>
-      </c>
+        <v>-658900000</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>-118700000</v>
+        <v>-148800000</v>
       </c>
       <c r="N4" t="n">
-        <v>-15900000</v>
-      </c>
-      <c r="O4" t="n">
+        <v>-16500000</v>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="n">
+        <v>-472900000</v>
+      </c>
+      <c r="S4" t="n">
+        <v>-472900000</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-472900000</v>
+      </c>
+      <c r="U4" t="n">
         <v>0</v>
       </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="n">
+      <c r="V4" t="n">
+        <v>291300000</v>
+      </c>
+      <c r="W4" t="n">
+        <v>569000000</v>
+      </c>
+      <c r="X4" t="n">
+        <v>60500000</v>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="n">
+        <v>-338200000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>18600000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-356800000</v>
+      </c>
+      <c r="AD4" t="n">
         <v>0</v>
       </c>
-      <c r="R4" t="n">
-        <v>-695500000</v>
-      </c>
-      <c r="S4" t="n">
-        <v>-695500000</v>
-      </c>
-      <c r="T4" t="n">
-        <v>-735500000</v>
-      </c>
-      <c r="U4" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="V4" t="n">
-        <v>5200000</v>
-      </c>
-      <c r="W4" t="n">
-        <v>-917200000</v>
-      </c>
-      <c r="X4" t="n">
-        <v>37000000</v>
-      </c>
-      <c r="Y4" t="n">
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="n">
         <v>0</v>
       </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>885400000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1684900000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>-799500000</v>
-      </c>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="n">
-        <v>364900000</v>
+        <v>384800000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-157800000</v>
+        <v>-46700000</v>
       </c>
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="n">
-        <v>-81500000</v>
+        <v>-219900000</v>
       </c>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="n">
-        <v>180400000</v>
+        <v>193800000</v>
       </c>
       <c r="AO4" t="n">
-        <v>-190000000</v>
+        <v>-998900000</v>
       </c>
       <c r="AP4" t="n">
-        <v>146800000</v>
+        <v>305000000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>146800000</v>
+        <v>305000000</v>
       </c>
       <c r="AR4" t="n">
-        <v>912700000</v>
+        <v>3912600000</v>
       </c>
       <c r="AS4" t="n">
-        <v>-445700000</v>
+        <v>-2761100000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>607300000</v>
-      </c>
-      <c r="C5" t="n">
+        <v>725500000</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>-223000000</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>432100000</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-43500000</v>
+      </c>
+      <c r="I5" t="n">
+        <v>201500000</v>
+      </c>
+      <c r="J5" t="n">
+        <v>230600000</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-417100000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-3200000</v>
+      </c>
+      <c r="M5" t="n">
+        <v>-154600000</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-16500000</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="n">
+        <v>-223000000</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-223000000</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-223000000</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="n">
+        <v>-77800000</v>
+      </c>
+      <c r="W5" t="n">
+        <v>181000000</v>
+      </c>
+      <c r="X5" t="n">
+        <v>34800000</v>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="n">
+        <v>-291200000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>330200000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-621400000</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-2400000</v>
+      </c>
+      <c r="AE5" t="n">
         <v>0</v>
       </c>
-      <c r="D5" t="n">
-        <v>-1267500000</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1354400000</v>
-      </c>
-      <c r="F5" t="n">
-        <v>660800000</v>
-      </c>
-      <c r="G5" t="n">
-        <v>676700000</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="n">
-        <v>583300000</v>
-      </c>
-      <c r="J5" t="n">
-        <v>93400000</v>
-      </c>
-      <c r="K5" t="n">
-        <v>174600000</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1314700000</v>
-      </c>
-      <c r="M5" t="n">
-        <v>-151800000</v>
-      </c>
-      <c r="N5" t="n">
-        <v>-358900000</v>
-      </c>
-      <c r="O5" t="n">
-        <v>660800000</v>
-      </c>
-      <c r="P5" t="n">
+      <c r="AF5" t="n">
+        <v>-2400000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>725500000</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-79700000</v>
+      </c>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="n">
+        <v>131400000</v>
+      </c>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="n">
+        <v>536600000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>51700000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>39600000</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>39600000</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>636900000</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>-591000000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>793600000</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>-999800000</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>442200000</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="n">
+        <v>432100000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>10100000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-488300000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>698800000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-150400000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-16500000</v>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="n">
+        <v>-999800000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-999800000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-999800000</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>-295200000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>356800000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>15800000</v>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="n">
+        <v>-1015700000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>355600000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-1371300000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>347900000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>347900000</v>
+      </c>
+      <c r="AF6" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>660800000</v>
-      </c>
-      <c r="R5" t="n">
-        <v>-1267500000</v>
-      </c>
-      <c r="S5" t="n">
-        <v>-1267500000</v>
-      </c>
-      <c r="T5" t="n">
-        <v>-1267500000</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1354400000</v>
-      </c>
-      <c r="V5" t="n">
-        <v>-688500000</v>
-      </c>
-      <c r="W5" t="n">
-        <v>-581600000</v>
-      </c>
-      <c r="X5" t="n">
-        <v>9700000</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>9700000</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>9700000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>-126300000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>635700000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>-762000000</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>9800000</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>9800000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>607300000</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>-28900000</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>9700000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>-151800000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>-14100000</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>-13300000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>-800000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>522300000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>857400000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>213900000</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>213900000</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>-1862300000</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>919000000</v>
+      <c r="AG6" t="n">
+        <v>793600000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-9500000</v>
+      </c>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="n">
+        <v>135500000</v>
+      </c>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="n">
+        <v>128600000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>-823900000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>404400000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>404400000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-221100000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1179600000</v>
       </c>
     </row>
   </sheetData>
@@ -3444,7 +3661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP2"/>
+  <dimension ref="A1:EM2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3620,560 +3837,545 @@
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>dividendRate</t>
+          <t>beta</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>dividendYield</t>
+          <t>trailingPE</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
         <is>
-          <t>exDividendDate</t>
+          <t>volume</t>
         </is>
       </c>
       <c r="AL1" t="inlineStr">
         <is>
-          <t>payoutRatio</t>
+          <t>regularMarketVolume</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>beta</t>
+          <t>averageVolume</t>
         </is>
       </c>
       <c r="AN1" t="inlineStr">
         <is>
-          <t>volume</t>
+          <t>averageVolume10days</t>
         </is>
       </c>
       <c r="AO1" t="inlineStr">
         <is>
-          <t>regularMarketVolume</t>
+          <t>averageDailyVolume10Day</t>
         </is>
       </c>
       <c r="AP1" t="inlineStr">
         <is>
-          <t>averageVolume</t>
+          <t>bid</t>
         </is>
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
-          <t>averageVolume10days</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AR1" t="inlineStr">
         <is>
-          <t>averageDailyVolume10Day</t>
+          <t>marketCap</t>
         </is>
       </c>
       <c r="AS1" t="inlineStr">
         <is>
-          <t>bid</t>
+          <t>nonDilutedMarketCap</t>
         </is>
       </c>
       <c r="AT1" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>fiftyTwoWeekLow</t>
         </is>
       </c>
       <c r="AU1" t="inlineStr">
         <is>
-          <t>marketCap</t>
+          <t>fiftyTwoWeekHigh</t>
         </is>
       </c>
       <c r="AV1" t="inlineStr">
         <is>
-          <t>nonDilutedMarketCap</t>
+          <t>allTimeHigh</t>
         </is>
       </c>
       <c r="AW1" t="inlineStr">
         <is>
-          <t>fiftyTwoWeekLow</t>
+          <t>allTimeLow</t>
         </is>
       </c>
       <c r="AX1" t="inlineStr">
         <is>
-          <t>fiftyTwoWeekHigh</t>
+          <t>priceToSalesTrailing12Months</t>
         </is>
       </c>
       <c r="AY1" t="inlineStr">
         <is>
-          <t>allTimeHigh</t>
+          <t>fiftyDayAverage</t>
         </is>
       </c>
       <c r="AZ1" t="inlineStr">
         <is>
-          <t>allTimeLow</t>
+          <t>twoHundredDayAverage</t>
         </is>
       </c>
       <c r="BA1" t="inlineStr">
         <is>
-          <t>priceToSalesTrailing12Months</t>
+          <t>trailingAnnualDividendRate</t>
         </is>
       </c>
       <c r="BB1" t="inlineStr">
         <is>
-          <t>fiftyDayAverage</t>
+          <t>trailingAnnualDividendYield</t>
         </is>
       </c>
       <c r="BC1" t="inlineStr">
         <is>
-          <t>twoHundredDayAverage</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="BD1" t="inlineStr">
         <is>
-          <t>trailingAnnualDividendRate</t>
+          <t>tradeable</t>
         </is>
       </c>
       <c r="BE1" t="inlineStr">
         <is>
-          <t>trailingAnnualDividendYield</t>
+          <t>enterpriseValue</t>
         </is>
       </c>
       <c r="BF1" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>profitMargins</t>
         </is>
       </c>
       <c r="BG1" t="inlineStr">
         <is>
-          <t>tradeable</t>
+          <t>floatShares</t>
         </is>
       </c>
       <c r="BH1" t="inlineStr">
         <is>
-          <t>enterpriseValue</t>
+          <t>sharesOutstanding</t>
         </is>
       </c>
       <c r="BI1" t="inlineStr">
         <is>
-          <t>profitMargins</t>
+          <t>heldPercentInsiders</t>
         </is>
       </c>
       <c r="BJ1" t="inlineStr">
         <is>
-          <t>floatShares</t>
+          <t>heldPercentInstitutions</t>
         </is>
       </c>
       <c r="BK1" t="inlineStr">
         <is>
-          <t>sharesOutstanding</t>
+          <t>impliedSharesOutstanding</t>
         </is>
       </c>
       <c r="BL1" t="inlineStr">
         <is>
-          <t>heldPercentInsiders</t>
+          <t>bookValue</t>
         </is>
       </c>
       <c r="BM1" t="inlineStr">
         <is>
-          <t>heldPercentInstitutions</t>
+          <t>priceToBook</t>
         </is>
       </c>
       <c r="BN1" t="inlineStr">
         <is>
-          <t>impliedSharesOutstanding</t>
+          <t>lastFiscalYearEnd</t>
         </is>
       </c>
       <c r="BO1" t="inlineStr">
         <is>
-          <t>bookValue</t>
+          <t>nextFiscalYearEnd</t>
         </is>
       </c>
       <c r="BP1" t="inlineStr">
         <is>
-          <t>priceToBook</t>
+          <t>mostRecentQuarter</t>
         </is>
       </c>
       <c r="BQ1" t="inlineStr">
         <is>
-          <t>lastFiscalYearEnd</t>
+          <t>netIncomeToCommon</t>
         </is>
       </c>
       <c r="BR1" t="inlineStr">
         <is>
-          <t>nextFiscalYearEnd</t>
+          <t>trailingEps</t>
         </is>
       </c>
       <c r="BS1" t="inlineStr">
         <is>
-          <t>mostRecentQuarter</t>
+          <t>enterpriseToRevenue</t>
         </is>
       </c>
       <c r="BT1" t="inlineStr">
         <is>
-          <t>netIncomeToCommon</t>
+          <t>enterpriseToEbitda</t>
         </is>
       </c>
       <c r="BU1" t="inlineStr">
         <is>
-          <t>trailingEps</t>
+          <t>52WeekChange</t>
         </is>
       </c>
       <c r="BV1" t="inlineStr">
         <is>
-          <t>enterpriseToRevenue</t>
+          <t>SandP52WeekChange</t>
         </is>
       </c>
       <c r="BW1" t="inlineStr">
         <is>
-          <t>enterpriseToEbitda</t>
+          <t>lastDividendValue</t>
         </is>
       </c>
       <c r="BX1" t="inlineStr">
         <is>
-          <t>52WeekChange</t>
+          <t>lastDividendDate</t>
         </is>
       </c>
       <c r="BY1" t="inlineStr">
         <is>
-          <t>SandP52WeekChange</t>
+          <t>quoteType</t>
         </is>
       </c>
       <c r="BZ1" t="inlineStr">
         <is>
-          <t>lastDividendValue</t>
+          <t>currentPrice</t>
         </is>
       </c>
       <c r="CA1" t="inlineStr">
         <is>
-          <t>lastDividendDate</t>
+          <t>recommendationKey</t>
         </is>
       </c>
       <c r="CB1" t="inlineStr">
         <is>
-          <t>quoteType</t>
+          <t>totalCash</t>
         </is>
       </c>
       <c r="CC1" t="inlineStr">
         <is>
-          <t>currentPrice</t>
+          <t>totalCashPerShare</t>
         </is>
       </c>
       <c r="CD1" t="inlineStr">
         <is>
-          <t>recommendationKey</t>
+          <t>ebitda</t>
         </is>
       </c>
       <c r="CE1" t="inlineStr">
         <is>
-          <t>totalCash</t>
+          <t>totalDebt</t>
         </is>
       </c>
       <c r="CF1" t="inlineStr">
         <is>
-          <t>totalCashPerShare</t>
+          <t>quickRatio</t>
         </is>
       </c>
       <c r="CG1" t="inlineStr">
         <is>
-          <t>ebitda</t>
+          <t>currentRatio</t>
         </is>
       </c>
       <c r="CH1" t="inlineStr">
         <is>
-          <t>totalDebt</t>
+          <t>totalRevenue</t>
         </is>
       </c>
       <c r="CI1" t="inlineStr">
         <is>
-          <t>quickRatio</t>
+          <t>debtToEquity</t>
         </is>
       </c>
       <c r="CJ1" t="inlineStr">
         <is>
-          <t>currentRatio</t>
+          <t>revenuePerShare</t>
         </is>
       </c>
       <c r="CK1" t="inlineStr">
         <is>
-          <t>totalRevenue</t>
+          <t>returnOnAssets</t>
         </is>
       </c>
       <c r="CL1" t="inlineStr">
         <is>
-          <t>debtToEquity</t>
+          <t>returnOnEquity</t>
         </is>
       </c>
       <c r="CM1" t="inlineStr">
         <is>
-          <t>revenuePerShare</t>
+          <t>grossProfits</t>
         </is>
       </c>
       <c r="CN1" t="inlineStr">
         <is>
-          <t>returnOnAssets</t>
+          <t>freeCashflow</t>
         </is>
       </c>
       <c r="CO1" t="inlineStr">
         <is>
-          <t>returnOnEquity</t>
+          <t>operatingCashflow</t>
         </is>
       </c>
       <c r="CP1" t="inlineStr">
         <is>
-          <t>grossProfits</t>
+          <t>revenueGrowth</t>
         </is>
       </c>
       <c r="CQ1" t="inlineStr">
         <is>
-          <t>freeCashflow</t>
+          <t>grossMargins</t>
         </is>
       </c>
       <c r="CR1" t="inlineStr">
         <is>
-          <t>operatingCashflow</t>
+          <t>ebitdaMargins</t>
         </is>
       </c>
       <c r="CS1" t="inlineStr">
         <is>
-          <t>revenueGrowth</t>
+          <t>operatingMargins</t>
         </is>
       </c>
       <c r="CT1" t="inlineStr">
         <is>
-          <t>grossMargins</t>
+          <t>financialCurrency</t>
         </is>
       </c>
       <c r="CU1" t="inlineStr">
         <is>
-          <t>ebitdaMargins</t>
+          <t>symbol</t>
         </is>
       </c>
       <c r="CV1" t="inlineStr">
         <is>
-          <t>operatingMargins</t>
+          <t>language</t>
         </is>
       </c>
       <c r="CW1" t="inlineStr">
         <is>
-          <t>financialCurrency</t>
+          <t>region</t>
         </is>
       </c>
       <c r="CX1" t="inlineStr">
         <is>
-          <t>symbol</t>
+          <t>typeDisp</t>
         </is>
       </c>
       <c r="CY1" t="inlineStr">
         <is>
-          <t>language</t>
+          <t>quoteSourceName</t>
         </is>
       </c>
       <c r="CZ1" t="inlineStr">
         <is>
-          <t>region</t>
+          <t>triggerable</t>
         </is>
       </c>
       <c r="DA1" t="inlineStr">
         <is>
-          <t>typeDisp</t>
+          <t>customPriceAlertConfidence</t>
         </is>
       </c>
       <c r="DB1" t="inlineStr">
         <is>
-          <t>quoteSourceName</t>
+          <t>earningsTimestampStart</t>
         </is>
       </c>
       <c r="DC1" t="inlineStr">
         <is>
-          <t>triggerable</t>
+          <t>earningsTimestampEnd</t>
         </is>
       </c>
       <c r="DD1" t="inlineStr">
         <is>
-          <t>customPriceAlertConfidence</t>
+          <t>isEarningsDateEstimate</t>
         </is>
       </c>
       <c r="DE1" t="inlineStr">
         <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>earningsTimestamp</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
         <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>earningsTimestamp</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
       <c r="EM1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -4190,10 +4392,8 @@
           <t>Berlin</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>14197</t>
-        </is>
+      <c r="C2" t="n">
+        <v>14197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -4274,7 +4474,7 @@
         <v>8</v>
       </c>
       <c r="V2" t="n">
-        <v>1780272000</v>
+        <v>1780531200</v>
       </c>
       <c r="W2" t="n">
         <v>1735603200</v>
@@ -4291,405 +4491,396 @@
         <v>2</v>
       </c>
       <c r="AA2" t="n">
-        <v>19.26</v>
+        <v>18.3</v>
       </c>
       <c r="AB2" t="n">
-        <v>19.36</v>
+        <v>18.12</v>
       </c>
       <c r="AC2" t="n">
-        <v>19.36</v>
+        <v>18.12</v>
       </c>
       <c r="AD2" t="n">
-        <v>19.36</v>
+        <v>18.12</v>
       </c>
       <c r="AE2" t="n">
-        <v>19.26</v>
+        <v>18.3</v>
       </c>
       <c r="AF2" t="n">
-        <v>19.36</v>
+        <v>18.12</v>
       </c>
       <c r="AG2" t="n">
-        <v>19.36</v>
+        <v>18.12</v>
       </c>
       <c r="AH2" t="n">
-        <v>19.36</v>
+        <v>18.12</v>
       </c>
       <c r="AI2" t="n">
+        <v>1.145</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>6.7158675</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>301</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>301</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>30</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>30</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>18.14</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>18.22</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>7224217088</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>7248032826</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>18.08</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>22.65</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>27.55</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>4.2303786</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>19.5192</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>20.59435</v>
+      </c>
+      <c r="BA2" t="n">
         <v>0.04</v>
       </c>
-      <c r="AJ2" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1779235200</v>
-      </c>
-      <c r="AL2" t="n">
+      <c r="BB2" t="n">
+        <v>0.0021857924</v>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="BD2" t="b">
         <v>0</v>
       </c>
-      <c r="AM2" t="n">
-        <v>1.178</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>20</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>20</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>19.06</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>7597335040</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>7676722609</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>19.36</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>22.65</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>27.55</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>4.4488697</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>19.9452</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>20.8118</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>0.04</v>
-      </c>
       <c r="BE2" t="n">
-        <v>0.002076843</v>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="BG2" t="b">
-        <v>0</v>
+        <v>15402780672</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>0.67137</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>30262323</v>
       </c>
       <c r="BH2" t="n">
-        <v>15680635904</v>
+        <v>396934985</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.67137</v>
+        <v>0.8687</v>
       </c>
       <c r="BJ2" t="n">
-        <v>30262323</v>
+        <v>0.02814</v>
       </c>
       <c r="BK2" t="n">
         <v>396934985</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.8687</v>
+        <v>35.682</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.02819</v>
+        <v>0.51006114</v>
       </c>
       <c r="BN2" t="n">
-        <v>396934985</v>
+        <v>1767139200</v>
       </c>
       <c r="BO2" t="n">
-        <v>35.682</v>
+        <v>1798675200</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.5364049</v>
+        <v>1767139200</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1767139200</v>
+        <v>1075200000</v>
       </c>
       <c r="BR2" t="n">
-        <v>1798675200</v>
+        <v>2.71</v>
       </c>
       <c r="BS2" t="n">
-        <v>1767139200</v>
+        <v>9.02</v>
       </c>
       <c r="BT2" t="n">
-        <v>1075200000</v>
+        <v>55.148</v>
       </c>
       <c r="BU2" t="n">
-        <v>-1.26</v>
+        <v>-0.14312798</v>
       </c>
       <c r="BV2" t="n">
-        <v>9.182</v>
+        <v>0.24487448</v>
       </c>
       <c r="BW2" t="n">
-        <v>56.143</v>
+        <v>0.04</v>
       </c>
       <c r="BX2" t="n">
-        <v>-0.0872038</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>0.27449715</v>
+        <v>1779235200</v>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
       </c>
       <c r="BZ2" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>1779235200</v>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>EQUITY</t>
-        </is>
+        <v>18.2</v>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="CB2" t="n">
+        <v>442200000</v>
       </c>
       <c r="CC2" t="n">
-        <v>19.14</v>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
+        <v>1.114</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>279300000</v>
       </c>
       <c r="CE2" t="n">
-        <v>442200000</v>
+        <v>8094199808</v>
       </c>
       <c r="CF2" t="n">
-        <v>1.114</v>
+        <v>0.382</v>
       </c>
       <c r="CG2" t="n">
-        <v>279300000</v>
+        <v>0.893</v>
       </c>
       <c r="CH2" t="n">
-        <v>8094199808</v>
+        <v>1707699968</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.382</v>
+        <v>55.459</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.893</v>
+        <v>4.302</v>
       </c>
       <c r="CK2" t="n">
-        <v>1707699968</v>
+        <v>0.0052300002</v>
       </c>
       <c r="CL2" t="n">
-        <v>55.459</v>
+        <v>0.07915</v>
       </c>
       <c r="CM2" t="n">
-        <v>4.302</v>
+        <v>860499968</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.0052300002</v>
+        <v>1106412544</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.07915</v>
+        <v>793600000</v>
       </c>
       <c r="CP2" t="n">
-        <v>860499968</v>
+        <v>-0.397</v>
       </c>
       <c r="CQ2" t="n">
-        <v>1106412544</v>
+        <v>0.5038899999999999</v>
       </c>
       <c r="CR2" t="n">
-        <v>793600000</v>
+        <v>0.16354999</v>
       </c>
       <c r="CS2" t="n">
-        <v>-0.397</v>
-      </c>
-      <c r="CT2" t="n">
-        <v>0.5038899999999999</v>
-      </c>
-      <c r="CU2" t="n">
-        <v>0.16354999</v>
-      </c>
-      <c r="CV2" t="n">
         <v>0.33325002</v>
       </c>
+      <c r="CT2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="CU2" t="inlineStr">
+        <is>
+          <t>1DWNI.MI</t>
+        </is>
+      </c>
+      <c r="CV2" t="inlineStr">
+        <is>
+          <t>en-US</t>
+        </is>
+      </c>
       <c r="CW2" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="CX2" t="inlineStr">
         <is>
-          <t>1DWNI.MI</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="CY2" t="inlineStr">
         <is>
-          <t>en-US</t>
-        </is>
-      </c>
-      <c r="CZ2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
+          <t>Delayed Quote</t>
+        </is>
+      </c>
+      <c r="CZ2" t="b">
+        <v>0</v>
       </c>
       <c r="DA2" t="inlineStr">
         <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="DB2" t="inlineStr">
-        <is>
-          <t>Delayed Quote</t>
-        </is>
-      </c>
-      <c r="DC2" t="b">
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="DB2" t="n">
+        <v>1778599800</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>1778599800</v>
+      </c>
+      <c r="DD2" t="b">
+        <v>1</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>-1.3191986</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>-0.06758467</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>-2.39435</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>-0.116262466</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>20</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DL2" t="b">
         <v>0</v>
       </c>
-      <c r="DD2" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="DE2" t="n">
-        <v>-0.6230573</v>
-      </c>
-      <c r="DF2" t="n">
-        <v>19.14</v>
-      </c>
-      <c r="DG2" t="inlineStr">
+      <c r="DM2" t="n">
+        <v>-0.54643977</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DQ2" t="n">
+        <v>1780902682</v>
+      </c>
+      <c r="DR2" t="inlineStr">
         <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="DH2" t="inlineStr">
+      <c r="DS2" t="inlineStr">
         <is>
           <t>finmb_5647053</t>
         </is>
       </c>
-      <c r="DI2" t="inlineStr">
+      <c r="DT2" t="inlineStr">
         <is>
           <t>Europe/Rome</t>
         </is>
       </c>
-      <c r="DJ2" t="inlineStr">
+      <c r="DU2" t="inlineStr">
         <is>
           <t>CEST</t>
         </is>
       </c>
-      <c r="DK2" t="n">
+      <c r="DV2" t="n">
         <v>7200000</v>
       </c>
-      <c r="DL2" t="inlineStr">
+      <c r="DW2" t="inlineStr">
         <is>
           <t>it_market</t>
         </is>
       </c>
-      <c r="DM2" t="b">
+      <c r="DX2" t="b">
         <v>0</v>
       </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DO2" t="b">
+      <c r="DY2" t="b">
         <v>0</v>
       </c>
-      <c r="DP2" t="inlineStr">
+      <c r="DZ2" t="n">
+        <v>1704873600000</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>-0.099998474</v>
+      </c>
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>18.12 - 18.12</t>
+        </is>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="ED2" t="n">
+        <v>14</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>0.12000084</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>0.0066372147</v>
+      </c>
+      <c r="EG2" t="inlineStr">
+        <is>
+          <t>18.08 - 22.65</t>
+        </is>
+      </c>
+      <c r="EH2" t="n">
+        <v>-4.449999</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>-0.19646795</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>-14.312798</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>1774456200</v>
+      </c>
+      <c r="EL2" t="inlineStr">
         <is>
           <t>DEUTSCHE WOHNEN</t>
         </is>
       </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DR2" t="n">
-        <v>1780322099</v>
-      </c>
-      <c r="DS2" t="inlineStr">
-        <is>
-          <t>Milan</t>
-        </is>
-      </c>
-      <c r="DT2" t="n">
-        <v>10</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>-0.22000122</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>-0.011363699</v>
-      </c>
-      <c r="DW2" t="inlineStr">
-        <is>
-          <t>19.36 - 22.65</t>
-        </is>
-      </c>
-      <c r="DX2" t="n">
-        <v>-3.5100002</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>-0.1549669</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>-8.72038</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>1774456200</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>1778599800</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>1778599800</v>
-      </c>
-      <c r="ED2" t="b">
-        <v>1</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>-1.26</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>-0.8052006</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>-0.040370643</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>-1.6718006</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>-0.08032945499999999</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>20</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EL2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>1704873600000</v>
-      </c>
-      <c r="EN2" t="n">
-        <v>-0.12000084</v>
-      </c>
-      <c r="EO2" t="inlineStr">
-        <is>
-          <t>19.36 - 19.36</t>
-        </is>
-      </c>
-      <c r="EP2" t="inlineStr"/>
+      <c r="EM2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
